--- a/Plantilla_Test_2025.xlsx
+++ b/Plantilla_Test_2025.xlsx
@@ -17,6 +17,8 @@
     <sheet name="ENTREVISTAS_RETIRO" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="SINIESTRO" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="FUEROS_SALUD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TALENTO_DISCIPLINARIO" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="BIENESTAR_ACTIVIDADES" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1759,6 +1761,1453 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>NIT</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Numdocumento</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Acción</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>800.555.666-3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>106109276</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Diego López</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Auxiliar Logístico</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Daño a equipos</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Llamado de atención verbal</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>800.555.666-3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>106386599</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Juan López</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Tardanza reiterada</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Llamado de atención verbal</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>106826802</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fabio Martínez</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Daño a equipos</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Llamado de atención verbal</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>108617351</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Andrés Torres</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Daño a equipos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Llamado de atención escrito</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>800.555.666-3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Textiles Oriente S.A.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>107299549</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Juan Torres</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Almacenista</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Incumplimiento de normas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Suspensión 1 día</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>104717761</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Omar Hernández</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Tardanza reiterada</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Suspensión 1 día</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>104500083</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Diego Rodríguez</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Incumplimiento de normas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Descargo escrito</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Archivado</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>109650500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>María Sánchez</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Incumplimiento de normas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Suspensión 3 días</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>107456189</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Diego López</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Técnico</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Conducta inapropiada</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Plan de mejora</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>104698305</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fabio Martínez</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Conducta inapropiada</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Suspensión 1 día</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Archivado</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>108753556</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Claudia Vargas</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bajo rendimiento</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Suspensión 3 días</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>103424848</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fabio Martínez</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ausentismo injustificado</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Llamado de atención escrito</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>105104636</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Diana Torres</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bajo rendimiento</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Plan de mejora</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Archivado</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>108940630</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Claudia Vargas</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Tardanza reiterada</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Llamado de atención escrito</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>800.333.444-2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Agro Norte Ltda</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>102063906</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pedro López</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Operario de Producción</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ausentismo injustificado</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Suspensión 1 día</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>En seguimiento</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Sin novedad adicional</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>NIT</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Personas</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Impacto</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bienvenida 2025 — Celebración inicio de año</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>72</v>
+      </c>
+      <c r="I2" t="n">
+        <v>82</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Diego Castro</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Día de la Amistad — Integración virtual</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Andrés Morales</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Día de la Mujer — Reconocimiento y charla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Híbrido</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>63</v>
+      </c>
+      <c r="I4" t="n">
+        <v>71</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Claudia Soto</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pausas activas saludables</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>91</v>
+      </c>
+      <c r="I5" t="n">
+        <v>85</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Diego Castro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Celebración Día de la Madre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I6" t="n">
+        <v>80</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Andrés Morales</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Taller Bienestar Emocional y Estrés</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>65</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Claudia Soto</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Actividad deportiva — Campeonato interno</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>110</v>
+      </c>
+      <c r="I8" t="n">
+        <v>90</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Diego Castro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>800.111.222-1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TechSolutions S.A.S</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Charla nutrición y hábitos saludables</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>74</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Natalia Herrera</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Actividad completada exitosamente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2218,7 +3667,6 @@
       <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2229,8 +3677,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -2515,8 +3961,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -2947,8 +4391,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -3364,7 +4806,6 @@
       <c r="W11" t="n">
         <v>6</v>
       </c>
-      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3375,8 +4816,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -3500,7 +4939,6 @@
       <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3511,8 +4949,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -3928,7 +5364,6 @@
       <c r="W15" t="n">
         <v>2</v>
       </c>
-      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -3939,8 +5374,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -4356,7 +5789,6 @@
       <c r="W18" t="n">
         <v>6</v>
       </c>
-      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -4367,8 +5799,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -4507,8 +5937,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -5523,8 +6951,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -5794,7 +7220,6 @@
       <c r="W28" t="n">
         <v>4</v>
       </c>
-      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -5805,8 +7230,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -5930,7 +7353,6 @@
       <c r="W29" t="n">
         <v>0</v>
       </c>
-      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -5941,8 +7363,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -7234,7 +8654,6 @@
       <c r="W38" t="n">
         <v>3</v>
       </c>
-      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -7245,8 +8664,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -7969,8 +9386,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -8532,7 +9947,6 @@
       <c r="W47" t="n">
         <v>5</v>
       </c>
-      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -8543,8 +9957,6 @@
           <t>2025-06-22</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
           <t>Conforme</t>
@@ -13435,7 +14847,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13506,7 +14917,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13577,7 +14987,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13648,7 +15057,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13719,7 +15127,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13790,7 +15197,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13861,7 +15267,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13932,7 +15337,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14003,7 +15407,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14074,7 +15477,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14145,7 +15547,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14216,7 +15617,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14287,7 +15687,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14358,7 +15757,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14429,7 +15827,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14500,7 +15897,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14571,7 +15967,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14642,7 +16037,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14713,7 +16107,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14784,7 +16177,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14855,7 +16247,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14926,7 +16317,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14997,7 +16387,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15068,7 +16457,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15139,7 +16527,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15210,7 +16597,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15281,7 +16667,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15352,7 +16737,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15423,7 +16807,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15494,7 +16877,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15565,7 +16947,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15636,7 +17017,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15707,7 +17087,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15778,7 +17157,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15849,7 +17227,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15920,7 +17297,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15991,7 +17367,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16062,7 +17437,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16133,7 +17507,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16204,7 +17577,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16275,7 +17647,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16346,7 +17717,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16417,7 +17787,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16488,7 +17857,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16559,7 +17927,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16630,7 +17997,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16701,7 +18067,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16772,7 +18137,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16843,7 +18207,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16914,7 +18277,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16985,7 +18347,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17056,7 +18417,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17127,7 +18487,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17198,7 +18557,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17269,7 +18627,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17340,7 +18697,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17411,7 +18767,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17482,7 +18837,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17553,7 +18907,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17624,7 +18977,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17695,7 +19047,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17766,7 +19117,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17837,7 +19187,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17908,7 +19257,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17979,7 +19327,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18050,7 +19397,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18121,7 +19467,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18192,7 +19537,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18263,7 +19607,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18334,7 +19677,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18405,7 +19747,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18476,7 +19817,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18547,7 +19887,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18618,7 +19957,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18689,7 +20027,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18760,7 +20097,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18831,7 +20167,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18902,7 +20237,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18973,7 +20307,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19044,7 +20377,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19115,7 +20447,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -19186,7 +20517,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19257,7 +20587,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19328,7 +20657,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19399,7 +20727,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19470,7 +20797,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19541,7 +20867,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19612,7 +20937,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19683,7 +21007,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19754,7 +21077,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19825,7 +21147,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19896,7 +21217,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19967,7 +21287,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -20038,7 +21357,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -20109,7 +21427,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -20180,7 +21497,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -20251,7 +21567,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -20322,7 +21637,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20393,7 +21707,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -20464,7 +21777,6 @@
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28299,7 +29611,6 @@
           <t>Positiva</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28382,7 +29693,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28465,7 +29775,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28548,7 +29857,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28631,7 +29939,6 @@
           <t>Positiva</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28714,7 +30021,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28797,7 +30103,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28880,7 +30185,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28963,7 +30267,6 @@
           <t>Positiva</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29046,7 +30349,6 @@
           <t>Positiva</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29129,7 +30431,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29212,7 +30513,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29295,7 +30595,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29378,7 +30677,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29461,7 +30759,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29544,7 +30841,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29627,7 +30923,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29710,7 +31005,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -29793,7 +31087,6 @@
           <t>Negativa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -29876,7 +31169,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -29959,7 +31251,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -30042,7 +31333,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -30125,7 +31415,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -30208,7 +31497,6 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -30291,7 +31579,6 @@
           <t>Positiva</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Plantilla_Test_2025.xlsx
+++ b/Plantilla_Test_2025.xlsx
@@ -41,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002E4057"/>
         <bgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BA7517"/>
+        <bgColor rgb="00BA7517"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D9E75"/>
+        <bgColor rgb="001D9E75"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,9 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,244 +468,220 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HOJA</t>
+          <t>SELECCION</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DESCRIPCIÓN</t>
+          <t>Órdenes de servicio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COLUMNAS CLAVE</t>
+          <t>OrdenServicio, Estado (CERRADO/ABIERTO), Cumplimiento (A TIEMPO/INCUMPLIDA), EnReclutamiento, EnSeleccion, EnContratacion</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SELECCION</t>
+          <t>ROTACION</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Órdenes de servicio</t>
+          <t>Retiros de personal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OrdenServicio, Empresa, Ciudad, Estado, Cumplimiento, EnReclutamiento, EnSeleccion, EnContratacion</t>
+          <t>CausalRetiro, TipoRetiro, Genero, FechaRetiro, DiasLaborados</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ROTACION</t>
+          <t>PERSONAL_ACTIVO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retiros de personal</t>
+          <t>Plantilla activa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Numdocumento, CausalRetiro, FechaRetiro, TipoRetiro</t>
+          <t>Estado (Activo/ACTIVO), Cargo, AreaOperativa, FechaIngreso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PERSONAL_ACTIVO</t>
+          <t>AT_ACCIDENTES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plantilla activa</t>
+          <t>Accidentes de trabajo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Numdocumento, Estado (Activo/ACTIVO), Cargo, AreaOperativa</t>
+          <t>DiasIncapacidad, Peligro, ParteCuerpoAfectada, MecanismoAccidente</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AT_ACCIDENTES</t>
+          <t>EG_ENFERMEDADES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accidentes de trabajo</t>
+          <t>Enfermedades generales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Numdocumento, DiasIncapacidad, Peligro, ParteCuerpoAfectada</t>
+          <t>DiasIncapacidad, GrupoDiagnostico, Genero</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EG_ENFERMEDADES</t>
+          <t>FORMACION_SST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Enfermedades generales</t>
+          <t>Capacitaciones SST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Numdocumento, DiasIncapacidad, GrupoDiagnostico</t>
+          <t>Tema, FechaFormacion, PersonasProgramadas, PersonasAsistentes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FORMACION_SST</t>
+          <t>ENTREVISTAS_RETIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capacitaciones SST</t>
+          <t>Entrevistas de salida</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tema, FechaFormacion, PersonasProgramadas, PersonasAsistentes</t>
+          <t>MotivoRetiro, TratoJefe (Bueno/Regular/Deficiente), AplicoConocimientos (SI/NO)...</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENTREVISTAS_RETIRO</t>
+          <t>SINIESTRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entrevistas de salida</t>
+          <t>Siniestros laborales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MotivoRetiro, TratoJefe (Bueno/Regular/Deficiente), AplicoConocimientos (SI/NO)...</t>
+          <t>TipoSiniestro, Estado, Calificacion</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SINIESTRO</t>
+          <t>FUEROS_SALUD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siniestros laborales</t>
+          <t>Trabajadores con fuero</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TipoSiniestro, Estado, Calificacion</t>
+          <t>TipoFuero, NivelRiesgo, EstadoGestion</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FUEROS_SALUD</t>
+          <t>TALENTO_DISCIPLINARIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trabajadores con fuero</t>
+          <t>Procesos disciplinarios</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TipoFuero, NivelRiesgo, EstadoGestion</t>
+          <t>Cedula, FechaSolicitudMedida, FechaEntregaMedida, motivos (X), acciones (X), Observacion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TALENTO_DISCIPLINARIO</t>
+          <t>BIENESTAR_ACTIVIDADES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Procesos disciplinarios</t>
+          <t>Actividades bienestar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motivo, Acción, Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BIENESTAR_ACTIVIDADES</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Actividades bienestar</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Actividad, Personas, Impacto</t>
+          <t>Actividad, Fecha, Personas, Impacto, Medio</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• No renombres ni elimines hojas.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOTAS IMPORTANTES:</t>
+          <t>• PERSONAL_ACTIVO: Estado = 'Activo' o 'ACTIVO'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>• No renombres ni elimines hojas.</t>
+          <t>• TALENTO_DISCIPLINARIO: marcar X en las columnas de motivos y acciones que apliquen</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>• PERSONAL_ACTIVO: Estado = 'Activo' o 'ACTIVO'</t>
+          <t>• ENTREVISTAS_RETIRO: TratoJefe = Bueno / Regular / Deficiente</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
-        <is>
-          <t>• ENTREVISTAS_RETIRO: TratoJefe = Bueno / Regular / Deficiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>• Preguntas SI/NO: AplicoConocimientos, TrabajoEsperado, RetroalimentacionJefe, ElementosTrabajo, CondicionesFisicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
         <is>
           <t>• SELECCION: Cumplimiento = 'A TIEMPO' o 'INCUMPLIDA'</t>
         </is>
@@ -782,7 +776,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -852,73 +846,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Numdocumento</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nombres</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cedula</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Apellidos</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ciudad</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Acción</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FechaIngreso</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>FechaSolicitudMedida</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>FechaEntregaMedida</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>AusenciaInjustificada</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>UsocelularPlanta</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>MaltratoVerbal</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>OtroMotivo</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Descargos</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>DctoNomina</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>LlamadoAtencion</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>TerminacionContrato</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Observacion</t>
         </is>
       </c>
     </row>
@@ -930,7 +954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -940,50 +964,137 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1012345678</t>
+          <t>1113649333</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Juan García</t>
+          <t>MONTAÑO CUERO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Operario</t>
+          <t>JOSE G</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sede Norte</t>
+          <t>SOLDADOR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bogotá</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Incumplimiento horario</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Llamado de atención</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>PENDIENTE DEFINICION DE MEDIDA DISCIPLINARIA POR CLIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TechSolutions SAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>800.987.654-2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TechSolutions SAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14701956</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SANCHEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VICTOR HUGO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OPERARIO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2023-01-16</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>PENDIENTE DEFINICION DE MEDIDA DISCIPLINARIA POR CLIENTE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1000,62 +1111,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Ciudad</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Actividad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Impacto</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1069,7 +1180,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1129,7 +1240,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1375,7 +1486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1521,7 +1632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1653,7 +1764,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1885,7 +1996,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1961,7 +2072,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2128,7 +2239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2199,7 +2310,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2380,7 +2491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2566,7 +2677,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2725,7 +2836,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2782,7 +2893,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2965,7 +3076,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3077,7 +3188,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3189,7 +3300,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3392,7 +3503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>900.123.456-1</t>
+          <t>800.987.654-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
